--- a/QA_Defects_Template.xlsx
+++ b/QA_Defects_Template.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📖 Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defects Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📚 Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="📖 Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Defects Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="📚 Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -586,7 +586,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>4. Use dropdowns for Group Part and Problem Mode</t>
+          <t>4. Use dropdowns for Group Part, Problem Mode, and Supplier</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,15 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="C5:C10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Group Part" error="Please select a valid Group Part" promptTitle="Group Part" prompt="Select Group Part from dropdown" type="list">
       <formula1>"ELECTRIC &amp; ELEC.,PACKING,PIPING,PLASTIC,PRINTING,RAW MATERIAL,RUBBER,SHEET METAL,FOAM,SEALING,OTHERS"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Problem Mode" error="Please select a valid Problem Mode" promptTitle="Problem Mode" prompt="Select Problem Mode from dropdown" type="list">
       <formula1>"APPEARANCE NG,PART MISTAKE,DIMENSION NG,FUNCTION NG,LEAK"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Supplier" error="Please select a valid Supplier from the dropdown" promptTitle="Supplier" prompt="Select Supplier from dropdown (typing a value not in list will fail validation)" type="list">
+      <formula1>"KSV,AKUSAN,NISSEN CHEMITEC,PARADISE,BTD,C.G.,TTS PLASTIC,SAMBO,DEM,APT (Thailand),SUPERFAST,SAM NEO,TECHNO ASSOCIATE"</formula1>
     </dataValidation>
     <dataValidation sqref="A5:A10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Date" error="Please enter a valid date (YYYY-MM-DD)" promptTitle="Date" prompt="Enter date as YYYY-MM-DD (e.g., 2026-08-31)" type="date" operator="between">
       <formula1>2020-01-01</formula1>

--- a/QA_Defects_Template.xlsx
+++ b/QA_Defects_Template.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="📖 Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Defects Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="📚 Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,11 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,21 +36,6 @@
       <sz val="16"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="11"/>
@@ -63,6 +47,17 @@
       <sz val="14"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFD700"/>
       <sz val="14"/>
@@ -71,7 +66,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -81,20 +76,8 @@
     <fill>
       <patternFill patternType="solid"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
-        <bgColor rgb="00FFD700"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF8DC"/>
-        <bgColor rgb="00FFF8DC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,74 +86,40 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00888888"/>
-      </left>
-      <right style="thin">
-        <color rgb="00888888"/>
-      </right>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00888888"/>
-      </left>
-      <right style="thin">
-        <color rgb="00888888"/>
-      </right>
-      <top style="thin">
-        <color rgb="00888888"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00888888"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,7 +488,7 @@
   <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -550,7 +499,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -560,7 +509,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -605,7 +554,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -615,7 +564,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -646,7 +595,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -677,7 +626,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -708,7 +657,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -732,7 +681,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -766,287 +715,149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>⚡ 3K BATTERY - QA DEFECTS DATA ENTRY</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>📋 Fill in new defect records below. Dashboard auto-syncs every 30 seconds.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Found</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Group Part</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Problem Mode</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Part Name</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Part No</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="6" t="n">
         <v>46265</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>NISSEN CHEMITEC</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>PIPING</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>APPEARANCE NG</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>ELBOW PIPE 1/2</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>1P095004-1 K</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="H5" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Surface scratch on outer diameter</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>PARADISE</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>SHEET METAL</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>APPEARANCE NG</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>INSTALLATION PLATE</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>3P811368-1 A</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>Dent mark on corner</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>KSV</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>ELECTRIC &amp; ELEC.</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>LEAK</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>CAPACITOR 450V</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>VE101-22A</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>Insulation damage detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>AKUSAN</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>ELECTRIC &amp; ELEC.</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>APPEARANCE NG</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>CONNECTOR 2PIN</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>AC2019-A</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Pin misalignment</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>BTD</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>PLASTIC</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>PART MISTAKE</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>COVER HOUSING</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>4P022001-2 B</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>Wrong color (Black vs Grey)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <dataValidations count="5">
-    <dataValidation sqref="C5:C10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Group Part" error="Please select a valid Group Part" promptTitle="Group Part" prompt="Select Group Part from dropdown" type="list">
+  <dataValidations count="7">
+    <dataValidation sqref="A5:A10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThanOrEqual">
+      <formula1>2020-01-01</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"IN LINE,FINAL,INCOMING,OQA,CUSTOMER"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:C10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"KSV,AKUSAN,NISSEN CHEMITEC,PARADISE,BTD,C.G.,TTS PLASTIC,SAMBO,DEM,APT (Thailand),SUPERFAST,SAM NEO,TECHNO ASSOCIATE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"ELECTRIC &amp; ELEC.,PACKING,PIPING,PLASTIC,PRINTING,RAW MATERIAL,RUBBER,SHEET METAL,FOAM,SEALING,OTHERS"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Problem Mode" error="Please select a valid Problem Mode" promptTitle="Problem Mode" prompt="Select Problem Mode from dropdown" type="list">
+    <dataValidation sqref="E5:E10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"APPEARANCE NG,PART MISTAKE,DIMENSION NG,FUNCTION NG,LEAK"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:B10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Supplier" error="Please select a valid Supplier from the dropdown" promptTitle="Supplier" prompt="Select Supplier from dropdown (typing a value not in list will fail validation)" type="list">
-      <formula1>"KSV,AKUSAN,NISSEN CHEMITEC,PARADISE,BTD,C.G.,TTS PLASTIC,SAMBO,DEM,APT (Thailand),SUPERFAST,SAM NEO,TECHNO ASSOCIATE"</formula1>
+    <dataValidation sqref="H5:H10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Date" error="Please enter a valid date (YYYY-MM-DD)" promptTitle="Date" prompt="Enter date as YYYY-MM-DD (e.g., 2026-08-31)" type="date" operator="between">
-      <formula1>2020-01-01</formula1>
-      <formula2>2030-12-31</formula2>
-    </dataValidation>
-    <dataValidation sqref="G5:G10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number" promptTitle="Quantity" prompt="Enter quantity (positive integer)" type="whole" operator="greaterThan">
-      <formula1>0</formula1>
+    <dataValidation sqref="I5:I10000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"CRITICAL,MAJOR,MINOR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1062,201 +873,203 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Group Parts</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Problem Modes</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Suppliers</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>ELECTRIC &amp; ELEC.</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>APPEARANCE NG</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>NISSEN CHEMITEC</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>PACKING</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>PART MISTAKE</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>PARADISE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>PIPING</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>DIMENSION NG</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>BTD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>PLASTIC</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>FUNCTION NG</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>C.G.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>PRINTING</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>LEAK</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>TTS PLASTIC</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>RAW MATERIAL</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>KSV</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>RUBBER</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>AKUSAN</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>SHEET METAL</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>SAMBO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>FOAM</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>DEM</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>SEALING</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>APT (Thailand)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>OTHERS</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>SUPERFAST</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>SAM NEO</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>TECHNO ASSOCIATE</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>[ADD NEW...]</t>
         </is>
